--- a/06_Office_Related/01_NSO_work/06_SL_to_PIVOT_to_Compare_with_WP/02_GJ_WP_2026-27/SL 2.0/Dangs.xlsx
+++ b/06_Office_Related/01_NSO_work/06_SL_to_PIVOT_to_Compare_with_WP/02_GJ_WP_2026-27/SL 2.0/Dangs.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\2026-27\ICS\2.0   PLANNING 2026-27\Kharif 2026-27\2.0\2.0 planning 2026-27\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Grv\Grv\05 GIT\01_masterRepo\06_Office_Related\01_NSO_work\06_SL_to_PIVOT_to_Compare_with_WP\02_GJ_WP_2026-27\SL 2.0\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE7F3DCF-8F5E-42C3-B1B2-4E9EFE34BBDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D004842E-FB83-4928-990C-C54E13B2D7C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="central 2.0" sheetId="1" r:id="rId1"/>
@@ -28,8 +28,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -37,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="37">
   <si>
     <t xml:space="preserve">                               GUJARAT                                              STATEMENT NO. 4                                                  CENTRAL                                                                                      </t>
   </si>
@@ -145,6 +143,9 @@
   </si>
   <si>
     <t>GROUNDNUT</t>
+  </si>
+  <si>
+    <t>ZZZ</t>
   </si>
 </sst>
 </file>
@@ -359,31 +360,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -397,6 +374,30 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -679,99 +680,100 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:J19"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="10" max="10" width="14.28515625" customWidth="1"/>
+    <col min="3" max="3" width="13.88671875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="12" t="s">
+    <row r="1" spans="1:10" ht="18" x14ac:dyDescent="0.3">
+      <c r="A1" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
-      <c r="E1" s="12"/>
-      <c r="F1" s="12"/>
-      <c r="G1" s="12"/>
-      <c r="H1" s="12"/>
-      <c r="I1" s="12"/>
-      <c r="J1" s="12"/>
-    </row>
-    <row r="2" spans="1:10" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="12" t="s">
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
+      <c r="E1" s="18"/>
+      <c r="F1" s="18"/>
+      <c r="G1" s="18"/>
+      <c r="H1" s="18"/>
+      <c r="I1" s="18"/>
+      <c r="J1" s="18"/>
+    </row>
+    <row r="2" spans="1:10" ht="18" x14ac:dyDescent="0.3">
+      <c r="A2" s="18" t="s">
         <v>22</v>
       </c>
-      <c r="B2" s="12"/>
-      <c r="C2" s="12"/>
-      <c r="D2" s="12"/>
-      <c r="E2" s="12"/>
-      <c r="F2" s="12"/>
-      <c r="G2" s="12"/>
-      <c r="H2" s="12"/>
-      <c r="I2" s="12"/>
-      <c r="J2" s="12"/>
-    </row>
-    <row r="3" spans="1:10" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="13" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="13"/>
-      <c r="C3" s="13"/>
-      <c r="D3" s="13"/>
-      <c r="E3" s="13"/>
-      <c r="F3" s="13"/>
-      <c r="G3" s="13"/>
-      <c r="H3" s="13"/>
-      <c r="I3" s="13"/>
-      <c r="J3" s="13"/>
-    </row>
-    <row r="4" spans="1:10" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="14" t="s">
+      <c r="B2" s="18"/>
+      <c r="C2" s="18"/>
+      <c r="D2" s="18"/>
+      <c r="E2" s="18"/>
+      <c r="F2" s="18"/>
+      <c r="G2" s="18"/>
+      <c r="H2" s="18"/>
+      <c r="I2" s="18"/>
+      <c r="J2" s="18"/>
+    </row>
+    <row r="3" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A3" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="12"/>
+      <c r="C3" s="12"/>
+      <c r="D3" s="12"/>
+      <c r="E3" s="12"/>
+      <c r="F3" s="12"/>
+      <c r="G3" s="12"/>
+      <c r="H3" s="12"/>
+      <c r="I3" s="12"/>
+      <c r="J3" s="12"/>
+    </row>
+    <row r="4" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A4" s="19" t="s">
         <v>21</v>
       </c>
-      <c r="B4" s="15"/>
-      <c r="C4" s="18" t="s">
+      <c r="B4" s="20"/>
+      <c r="C4" s="23" t="s">
         <v>15</v>
       </c>
-      <c r="D4" s="20">
+      <c r="D4" s="17">
         <v>6</v>
       </c>
-      <c r="E4" s="20"/>
-      <c r="F4" s="20">
+      <c r="E4" s="17"/>
+      <c r="F4" s="17">
         <v>6</v>
       </c>
-      <c r="G4" s="20"/>
-      <c r="H4" s="20">
+      <c r="G4" s="17"/>
+      <c r="H4" s="17">
         <v>6</v>
       </c>
-      <c r="I4" s="20"/>
+      <c r="I4" s="17"/>
       <c r="J4" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="16"/>
-      <c r="B5" s="17"/>
-      <c r="C5" s="19"/>
-      <c r="D5" s="24" t="s">
+    <row r="5" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A5" s="21"/>
+      <c r="B5" s="22"/>
+      <c r="C5" s="24"/>
+      <c r="D5" s="16" t="s">
         <v>35</v>
       </c>
-      <c r="E5" s="24"/>
-      <c r="F5" s="24" t="s">
+      <c r="E5" s="16"/>
+      <c r="F5" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="G5" s="24"/>
-      <c r="H5" s="24" t="s">
+      <c r="G5" s="16"/>
+      <c r="H5" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="I5" s="24"/>
+      <c r="I5" s="16"/>
       <c r="J5" s="2">
         <f>D4+F4+H4</f>
         <v>18</v>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>5</v>
       </c>
@@ -801,7 +803,7 @@
       </c>
       <c r="J6" s="4"/>
     </row>
-    <row r="7" spans="1:10" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" ht="18" x14ac:dyDescent="0.3">
       <c r="A7" s="9" t="s">
         <v>19</v>
       </c>
@@ -826,7 +828,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:10" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A8" s="9" t="s">
         <v>17</v>
       </c>
@@ -855,12 +857,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="1:10" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="20" t="s">
+    <row r="9" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A9" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="B9" s="20"/>
-      <c r="C9" s="20"/>
+      <c r="B9" s="17"/>
+      <c r="C9" s="17"/>
       <c r="D9" s="5">
         <f>SUM(D7:D8)</f>
         <v>2</v>
@@ -881,25 +883,27 @@
         <v>6</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="13" t="s">
+    <row r="10" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A10" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="B10" s="13"/>
-      <c r="C10" s="13"/>
-      <c r="D10" s="13"/>
-      <c r="E10" s="13"/>
-      <c r="F10" s="13"/>
-      <c r="G10" s="13"/>
-      <c r="H10" s="13"/>
-      <c r="I10" s="13"/>
-      <c r="J10" s="13"/>
-    </row>
-    <row r="11" spans="1:10" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B10" s="12"/>
+      <c r="C10" s="12"/>
+      <c r="D10" s="12"/>
+      <c r="E10" s="12"/>
+      <c r="F10" s="12"/>
+      <c r="G10" s="12"/>
+      <c r="H10" s="12"/>
+      <c r="I10" s="12"/>
+      <c r="J10" s="12"/>
+    </row>
+    <row r="11" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="B11" s="4"/>
+      <c r="B11" s="4" t="s">
+        <v>36</v>
+      </c>
       <c r="C11" s="4" t="s">
         <v>23</v>
       </c>
@@ -918,11 +922,13 @@
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="1:10" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="B12" s="4"/>
+      <c r="B12" s="4" t="s">
+        <v>36</v>
+      </c>
       <c r="C12" s="4" t="s">
         <v>25</v>
       </c>
@@ -941,11 +947,13 @@
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="1:10" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="B13" s="4"/>
+      <c r="B13" s="4" t="s">
+        <v>36</v>
+      </c>
       <c r="C13" s="4" t="s">
         <v>26</v>
       </c>
@@ -964,11 +972,13 @@
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="1:10" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A14" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="B14" s="4"/>
+      <c r="B14" s="4" t="s">
+        <v>36</v>
+      </c>
       <c r="C14" s="4" t="s">
         <v>27</v>
       </c>
@@ -987,11 +997,13 @@
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="1:10" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A15" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="B15" s="4"/>
+      <c r="B15" s="4" t="s">
+        <v>36</v>
+      </c>
       <c r="C15" s="4" t="s">
         <v>28</v>
       </c>
@@ -1010,11 +1022,13 @@
         <v>2</v>
       </c>
     </row>
-    <row r="16" spans="1:10" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A16" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="B16" s="4"/>
+      <c r="B16" s="4" t="s">
+        <v>36</v>
+      </c>
       <c r="C16" s="4" t="s">
         <v>29</v>
       </c>
@@ -1033,7 +1047,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="17" spans="1:10" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A17" s="6"/>
       <c r="B17" s="7"/>
       <c r="C17" s="8"/>
@@ -1045,12 +1059,12 @@
       <c r="I17" s="5"/>
       <c r="J17" s="5"/>
     </row>
-    <row r="18" spans="1:10" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="21" t="s">
+    <row r="18" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A18" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="B18" s="22"/>
-      <c r="C18" s="23"/>
+      <c r="B18" s="14"/>
+      <c r="C18" s="15"/>
       <c r="D18" s="5">
         <f>SUM(D11:D16)</f>
         <v>4</v>
@@ -1071,12 +1085,12 @@
         <v>12</v>
       </c>
     </row>
-    <row r="19" spans="1:10" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="21" t="s">
+    <row r="19" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A19" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="B19" s="22"/>
-      <c r="C19" s="23"/>
+      <c r="B19" s="14"/>
+      <c r="C19" s="15"/>
       <c r="D19" s="5">
         <f>+D9+D18</f>
         <v>6</v>
@@ -1099,13 +1113,6 @@
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="A9:C9"/>
-    <mergeCell ref="A10:J10"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="D5:E5"/>
-    <mergeCell ref="F5:G5"/>
-    <mergeCell ref="H5:I5"/>
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A2:J2"/>
     <mergeCell ref="A3:J3"/>
@@ -1114,6 +1121,13 @@
     <mergeCell ref="D4:E4"/>
     <mergeCell ref="F4:G4"/>
     <mergeCell ref="H4:I4"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="A9:C9"/>
+    <mergeCell ref="A10:J10"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="D5:E5"/>
+    <mergeCell ref="F5:G5"/>
+    <mergeCell ref="H5:I5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1122,96 +1136,99 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:J16"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="3" max="3" width="13.21875" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="12" t="s">
+    <row r="1" spans="1:10" ht="18" x14ac:dyDescent="0.3">
+      <c r="A1" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
-      <c r="E1" s="12"/>
-      <c r="F1" s="12"/>
-      <c r="G1" s="12"/>
-      <c r="H1" s="12"/>
-      <c r="I1" s="12"/>
-      <c r="J1" s="12"/>
-    </row>
-    <row r="2" spans="1:10" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="12" t="s">
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
+      <c r="E1" s="18"/>
+      <c r="F1" s="18"/>
+      <c r="G1" s="18"/>
+      <c r="H1" s="18"/>
+      <c r="I1" s="18"/>
+      <c r="J1" s="18"/>
+    </row>
+    <row r="2" spans="1:10" ht="18" x14ac:dyDescent="0.3">
+      <c r="A2" s="18" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="12"/>
-      <c r="C2" s="12"/>
-      <c r="D2" s="12"/>
-      <c r="E2" s="12"/>
-      <c r="F2" s="12"/>
-      <c r="G2" s="12"/>
-      <c r="H2" s="12"/>
-      <c r="I2" s="12"/>
-      <c r="J2" s="12"/>
-    </row>
-    <row r="3" spans="1:10" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="13" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="13"/>
-      <c r="C3" s="13"/>
-      <c r="D3" s="13"/>
-      <c r="E3" s="13"/>
-      <c r="F3" s="13"/>
-      <c r="G3" s="13"/>
-      <c r="H3" s="13"/>
-      <c r="I3" s="13"/>
-      <c r="J3" s="13"/>
-    </row>
-    <row r="4" spans="1:10" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="14" t="s">
+      <c r="B2" s="18"/>
+      <c r="C2" s="18"/>
+      <c r="D2" s="18"/>
+      <c r="E2" s="18"/>
+      <c r="F2" s="18"/>
+      <c r="G2" s="18"/>
+      <c r="H2" s="18"/>
+      <c r="I2" s="18"/>
+      <c r="J2" s="18"/>
+    </row>
+    <row r="3" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A3" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="12"/>
+      <c r="C3" s="12"/>
+      <c r="D3" s="12"/>
+      <c r="E3" s="12"/>
+      <c r="F3" s="12"/>
+      <c r="G3" s="12"/>
+      <c r="H3" s="12"/>
+      <c r="I3" s="12"/>
+      <c r="J3" s="12"/>
+    </row>
+    <row r="4" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A4" s="19" t="s">
         <v>21</v>
       </c>
-      <c r="B4" s="15"/>
-      <c r="C4" s="18" t="s">
+      <c r="B4" s="20"/>
+      <c r="C4" s="23" t="s">
         <v>15</v>
       </c>
-      <c r="D4" s="20">
+      <c r="D4" s="17">
         <v>4</v>
       </c>
-      <c r="E4" s="20"/>
-      <c r="F4" s="20">
+      <c r="E4" s="17"/>
+      <c r="F4" s="17">
         <v>4</v>
       </c>
-      <c r="G4" s="20"/>
-      <c r="H4" s="20">
+      <c r="G4" s="17"/>
+      <c r="H4" s="17">
         <v>4</v>
       </c>
-      <c r="I4" s="20"/>
+      <c r="I4" s="17"/>
       <c r="J4" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="16"/>
-      <c r="B5" s="17"/>
-      <c r="C5" s="19"/>
-      <c r="D5" s="24" t="s">
+    <row r="5" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A5" s="21"/>
+      <c r="B5" s="22"/>
+      <c r="C5" s="24"/>
+      <c r="D5" s="16" t="s">
         <v>35</v>
       </c>
-      <c r="E5" s="24"/>
-      <c r="F5" s="24" t="s">
+      <c r="E5" s="16"/>
+      <c r="F5" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="G5" s="24"/>
-      <c r="H5" s="24" t="s">
+      <c r="G5" s="16"/>
+      <c r="H5" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="I5" s="24"/>
+      <c r="I5" s="16"/>
       <c r="J5" s="2">
         <f>D4+F4+H4</f>
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>5</v>
       </c>
@@ -1241,7 +1258,7 @@
       </c>
       <c r="J6" s="4"/>
     </row>
-    <row r="7" spans="1:10" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A7" s="11" t="s">
         <v>17</v>
       </c>
@@ -1263,7 +1280,7 @@
       <c r="I7" s="11"/>
       <c r="J7" s="4"/>
     </row>
-    <row r="8" spans="1:10" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10" ht="18" x14ac:dyDescent="0.3">
       <c r="A8" s="11" t="s">
         <v>17</v>
       </c>
@@ -1289,12 +1306,12 @@
       <c r="I8" s="11"/>
       <c r="J8" s="4"/>
     </row>
-    <row r="9" spans="1:10" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="20" t="s">
+    <row r="9" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A9" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="B9" s="20"/>
-      <c r="C9" s="20"/>
+      <c r="B9" s="17"/>
+      <c r="C9" s="17"/>
       <c r="D9" s="5">
         <f>SUM(D7:D8)</f>
         <v>4</v>
@@ -1314,25 +1331,27 @@
         <v>6</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="13" t="s">
+    <row r="10" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A10" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="B10" s="13"/>
-      <c r="C10" s="13"/>
-      <c r="D10" s="13"/>
-      <c r="E10" s="13"/>
-      <c r="F10" s="13"/>
-      <c r="G10" s="13"/>
-      <c r="H10" s="13"/>
-      <c r="I10" s="13"/>
-      <c r="J10" s="13"/>
-    </row>
-    <row r="11" spans="1:10" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B10" s="12"/>
+      <c r="C10" s="12"/>
+      <c r="D10" s="12"/>
+      <c r="E10" s="12"/>
+      <c r="F10" s="12"/>
+      <c r="G10" s="12"/>
+      <c r="H10" s="12"/>
+      <c r="I10" s="12"/>
+      <c r="J10" s="12"/>
+    </row>
+    <row r="11" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="B11" s="4"/>
+      <c r="B11" s="4" t="s">
+        <v>36</v>
+      </c>
       <c r="C11" s="4" t="s">
         <v>32</v>
       </c>
@@ -1348,11 +1367,13 @@
       </c>
       <c r="J11" s="4"/>
     </row>
-    <row r="12" spans="1:10" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="B12" s="4"/>
+      <c r="B12" s="4" t="s">
+        <v>36</v>
+      </c>
       <c r="C12" s="4" t="s">
         <v>33</v>
       </c>
@@ -1368,11 +1389,13 @@
       </c>
       <c r="J12" s="4"/>
     </row>
-    <row r="13" spans="1:10" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="B13" s="4"/>
+      <c r="B13" s="4" t="s">
+        <v>36</v>
+      </c>
       <c r="C13" s="4" t="s">
         <v>34</v>
       </c>
@@ -1388,7 +1411,7 @@
       <c r="I13" s="4"/>
       <c r="J13" s="4"/>
     </row>
-    <row r="14" spans="1:10" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A14" s="6"/>
       <c r="B14" s="7"/>
       <c r="C14" s="8"/>
@@ -1400,12 +1423,12 @@
       <c r="I14" s="5"/>
       <c r="J14" s="5"/>
     </row>
-    <row r="15" spans="1:10" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="21" t="s">
+    <row r="15" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A15" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="B15" s="22"/>
-      <c r="C15" s="23"/>
+      <c r="B15" s="14"/>
+      <c r="C15" s="15"/>
       <c r="D15" s="5">
         <f>SUM(D11:D14)</f>
         <v>0</v>
@@ -1425,12 +1448,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="16" spans="1:10" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="21" t="s">
+    <row r="16" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A16" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="B16" s="22"/>
-      <c r="C16" s="23"/>
+      <c r="B16" s="14"/>
+      <c r="C16" s="15"/>
       <c r="D16" s="5">
         <f>+D9+D15</f>
         <v>4</v>
@@ -1452,13 +1475,6 @@
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="A10:J10"/>
-    <mergeCell ref="A15:C15"/>
-    <mergeCell ref="A16:C16"/>
-    <mergeCell ref="D5:E5"/>
-    <mergeCell ref="F5:G5"/>
-    <mergeCell ref="H5:I5"/>
-    <mergeCell ref="A9:C9"/>
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A2:J2"/>
     <mergeCell ref="A3:J3"/>
@@ -1467,6 +1483,13 @@
     <mergeCell ref="D4:E4"/>
     <mergeCell ref="F4:G4"/>
     <mergeCell ref="H4:I4"/>
+    <mergeCell ref="A10:J10"/>
+    <mergeCell ref="A15:C15"/>
+    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="D5:E5"/>
+    <mergeCell ref="F5:G5"/>
+    <mergeCell ref="H5:I5"/>
+    <mergeCell ref="A9:C9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
